--- a/Dokumen/TAS/Analisis Data/ANGKET PENELITIAN TUGAS AKHIR SKRIPSI (Responses).xlsx
+++ b/Dokumen/TAS/Analisis Data/ANGKET PENELITIAN TUGAS AKHIR SKRIPSI (Responses).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\Dokumen\TAS\Analisis Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7AB9F3-5A9E-45C8-80F8-FA5525149C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D862E5-5515-4FED-8F6C-3F684D0F3373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1897,12 +1897,12 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'Form Responses 1'!$E$33</c:f>
+              <c:f>'Form Responses 1'!$G$33</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>20.433333333333334</c:v>
+                  <c:v>0.85138888888888886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1997,12 +1997,12 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'Form Responses 1'!$E$34</c:f>
+              <c:f>'Form Responses 1'!$G$34</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>29.833333333333332</c:v>
+                  <c:v>0.93229166666666663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2097,12 +2097,12 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'Form Responses 1'!$E$35</c:f>
+              <c:f>'Form Responses 1'!$G$35</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>20.5</c:v>
+                  <c:v>0.85416666666666663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2275,7 +2275,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4152,6 +4152,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Ahli Materi"/>
+      <sheetName val="Sheet3"/>
       <sheetName val="Ahli Media"/>
     </sheetNames>
     <sheetDataSet>
@@ -4173,6 +4174,7 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
